--- a/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:05:53+00:00</t>
+    <t>2026-09-14T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:56:03+00:00</t>
+    <t>2026-09-14T08:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$295</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12562" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11851" uniqueCount="1017">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:15:57+00:00</t>
+    <t>2026-10-14T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2462,15 +2462,12 @@
     <t>Beginn</t>
   </si>
   <si>
-    <t>Geschätztes oder tatsächliches Datum oder Zeitraum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung begonnen hat.</t>
   </si>
   <si>
     <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>KlinischRelevanterZeitraum</t>
   </si>
   <si>
@@ -2483,436 +2480,117 @@
     <t>FiveWs.init</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod</t>
-  </si>
-  <si>
-    <t>onsetPeriod</t>
-  </si>
-  <si>
-    <t>Beginn Zeitraum</t>
-  </si>
-  <si>
-    <t>Der Zeitraum, in dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.id</t>
+    <t>Condition.onset[x]:onsetDateTime</t>
+  </si>
+  <si>
+    <t>onsetDateTime</t>
+  </si>
+  <si>
+    <t>Beginn Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge</t>
+  </si>
+  <si>
+    <t>onsetAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
+</t>
+  </si>
+  <si>
+    <t>Erkrankungsbeginn als Alter</t>
+  </si>
+  <si>
+    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.id</t>
   </si>
   <si>
     <t>Condition.onset[x].id</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.extension</t>
+    <t>Condition.onset[x]:onsetAge.extension</t>
   </si>
   <si>
     <t>Condition.onset[x].extension</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von</t>
-  </si>
-  <si>
-    <t>lebensphase-von</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
+  </si>
+  <si>
+    <t>Lebensphase-Beginn</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://fhir.de/StructureDefinition/lebensphase}
 </t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.url</t>
+    <t>Lebensphase des Erkrankungsbeginns</t>
+  </si>
+  <si>
+    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.url</t>
   </si>
   <si>
     <t>http://fhir.de/StructureDefinition/lebensphase</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x]</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x]</t>
   </si>
   <si>
     <t>KlinischRelevanterZeitraum.Lebensphase.von</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Lebensphase</t>
   </si>
   <si>
     <t>http://fhir.de/ValueSet/lebensphase-de</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis</t>
-  </si>
-  <si>
-    <t>lebensphase-bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x]</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetDateTime</t>
-  </si>
-  <si>
-    <t>onsetDateTime</t>
-  </si>
-  <si>
-    <t>Beginn Datum</t>
-  </si>
-  <si>
-    <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge</t>
-  </si>
-  <si>
-    <t>onsetAge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age
-</t>
-  </si>
-  <si>
-    <t>Erkrankungsbeginn als Alter</t>
-  </si>
-  <si>
-    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase des Erkrankungsbeginns</t>
-  </si>
-  <si>
-    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding.id</t>
@@ -3088,14 +2766,10 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>dateTime
-AgePeriodRangestring</t>
-  </si>
-  <si>
-    <t>When in resolution/remission</t>
-  </si>
-  <si>
-    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+    <t>Ende</t>
+  </si>
+  <si>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung beendet wurde.</t>
   </si>
   <si>
     <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
@@ -3106,6 +2780,177 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>Ende Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung beendet wurde.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge</t>
+  </si>
+  <si>
+    <t>abatementAge</t>
+  </si>
+  <si>
+    <t>Erkrankungsende als Alter</t>
+  </si>
+  <si>
+    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase des Erkrankungsendes</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x]</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].code</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -3648,11 +3493,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR313"/>
+  <dimension ref="A1:AR295"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="79.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.20703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.52734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -32276,7 +32121,7 @@
         <v>81</v>
       </c>
       <c r="AE227" t="s" s="2">
-        <v>786</v>
+        <v>120</v>
       </c>
       <c r="AF227" t="s" s="2">
         <v>781</v>
@@ -32300,19 +32145,19 @@
         <v>81</v>
       </c>
       <c r="AM227" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AN227" t="s" s="2">
         <v>787</v>
       </c>
-      <c r="AN227" t="s" s="2">
+      <c r="AO227" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP227" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="AO227" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP227" t="s" s="2">
+      <c r="AQ227" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="AQ227" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="AR227" t="s" s="2">
         <v>81</v>
@@ -32320,13 +32165,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>781</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>81</v>
@@ -32348,13 +32193,13 @@
         <v>95</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>399</v>
+        <v>231</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="M228" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="M228" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="N228" t="s" s="2">
         <v>785</v>
@@ -32428,32 +32273,34 @@
         <v>81</v>
       </c>
       <c r="AM228" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AN228" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AO228" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP228" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AQ228" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="AR228" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="AN228" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="AO228" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP228" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="AQ228" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="AR228" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="229" hidden="true">
-      <c r="A229" t="s" s="2">
+      <c r="B229" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>796</v>
       </c>
-      <c r="B229" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
         <v>81</v>
       </c>
@@ -32465,24 +32312,26 @@
         <v>94</v>
       </c>
       <c r="H229" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J229" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>108</v>
+        <v>797</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>109</v>
+        <v>798</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N229" s="2"/>
+        <v>799</v>
+      </c>
+      <c r="N229" t="s" s="2">
+        <v>785</v>
+      </c>
       <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
         <v>81</v>
@@ -32531,7 +32380,7 @@
         <v>81</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>111</v>
+        <v>781</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>82</v>
@@ -32543,7 +32392,7 @@
         <v>81</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK229" t="s" s="2">
         <v>81</v>
@@ -32555,16 +32404,16 @@
         <v>81</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>81</v>
+        <v>787</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP229" t="s" s="2">
-        <v>81</v>
+        <v>788</v>
       </c>
       <c r="AQ229" t="s" s="2">
-        <v>81</v>
+        <v>789</v>
       </c>
       <c r="AR229" t="s" s="2">
         <v>81</v>
@@ -32572,21 +32421,21 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>81</v>
@@ -32598,17 +32447,15 @@
         <v>81</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N230" s="2"/>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>81</v>
@@ -32645,31 +32492,31 @@
         <v>81</v>
       </c>
       <c r="AB230" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC230" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE230" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="AK230" t="s" s="2">
         <v>81</v>
@@ -32696,44 +32543,44 @@
         <v>81</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H231" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J231" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>802</v>
+        <v>115</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>803</v>
+        <v>116</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>804</v>
+        <v>117</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
@@ -32771,31 +32618,31 @@
         <v>81</v>
       </c>
       <c r="AB231" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AC231" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AD231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE231" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>805</v>
+        <v>121</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>806</v>
+        <v>81</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK231" t="s" s="2">
         <v>81</v>
@@ -32804,7 +32651,7 @@
         <v>81</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>807</v>
+        <v>81</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>81</v>
@@ -32813,7 +32660,7 @@
         <v>81</v>
       </c>
       <c r="AP231" t="s" s="2">
-        <v>808</v>
+        <v>81</v>
       </c>
       <c r="AQ231" t="s" s="2">
         <v>81</v>
@@ -32824,12 +32671,14 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="C232" s="2"/>
+        <v>803</v>
+      </c>
+      <c r="C232" t="s" s="2">
+        <v>805</v>
+      </c>
       <c r="D232" t="s" s="2">
         <v>81</v>
       </c>
@@ -32850,15 +32699,17 @@
         <v>81</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>108</v>
+        <v>806</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="N232" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="N232" t="s" s="2">
+        <v>808</v>
+      </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
         <v>81</v>
@@ -32907,19 +32758,19 @@
         <v>81</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI232" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="AK232" t="s" s="2">
         <v>81</v>
@@ -32948,10 +32799,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -32962,7 +32813,7 @@
         <v>82</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>81</v>
@@ -32974,13 +32825,13 @@
         <v>81</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -33019,29 +32870,31 @@
         <v>81</v>
       </c>
       <c r="AB233" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC233" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC233" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE233" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>81</v>
@@ -33068,28 +32921,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="C234" t="s" s="2">
-        <v>816</v>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>81</v>
@@ -33098,15 +32949,17 @@
         <v>81</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>817</v>
+        <v>114</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>534</v>
+        <v>115</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N234" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N234" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
         <v>81</v>
@@ -33143,16 +32996,16 @@
         <v>81</v>
       </c>
       <c r="AB234" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AC234" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AD234" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE234" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AF234" t="s" s="2">
         <v>121</v>
@@ -33194,12 +33047,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="235" hidden="true">
+    <row r="235">
       <c r="A235" t="s" s="2">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -33207,13 +33060,13 @@
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G235" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H235" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I235" t="s" s="2">
         <v>81</v>
@@ -33222,22 +33075,24 @@
         <v>81</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N235" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="N235" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>81</v>
+        <v>815</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>81</v>
@@ -33279,10 +33134,10 @@
         <v>81</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>94</v>
@@ -33318,26 +33173,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="236" hidden="true">
+    <row r="236">
       <c r="A236" t="s" s="2">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H236" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I236" t="s" s="2">
         <v>81</v>
@@ -33346,17 +33201,15 @@
         <v>81</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N236" s="2"/>
       <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>81</v>
@@ -33393,31 +33246,31 @@
         <v>81</v>
       </c>
       <c r="AB236" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC236" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD236" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE236" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>201</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK236" t="s" s="2">
         <v>81</v>
@@ -33426,7 +33279,7 @@
         <v>81</v>
       </c>
       <c r="AM236" t="s" s="2">
-        <v>81</v>
+        <v>818</v>
       </c>
       <c r="AN236" t="s" s="2">
         <v>81</v>
@@ -33444,12 +33297,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -33457,13 +33310,13 @@
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G237" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H237" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I237" t="s" s="2">
         <v>81</v>
@@ -33472,24 +33325,22 @@
         <v>81</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N237" s="2"/>
       <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
-        <v>824</v>
+        <v>81</v>
       </c>
       <c r="S237" t="s" s="2">
         <v>81</v>
@@ -33531,10 +33382,10 @@
         <v>81</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>212</v>
+        <v>111</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>94</v>
@@ -33570,26 +33421,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H238" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I238" t="s" s="2">
         <v>81</v>
@@ -33598,15 +33449,17 @@
         <v>81</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>216</v>
+        <v>115</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N238" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N238" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>81</v>
@@ -33643,31 +33496,31 @@
         <v>81</v>
       </c>
       <c r="AB238" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AC238" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AD238" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE238" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>218</v>
+        <v>121</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>201</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK238" t="s" s="2">
         <v>81</v>
@@ -33676,7 +33529,7 @@
         <v>81</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>827</v>
+        <v>81</v>
       </c>
       <c r="AN238" t="s" s="2">
         <v>81</v>
@@ -33694,12 +33547,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="239" hidden="true">
+    <row r="239">
       <c r="A239" t="s" s="2">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -33707,31 +33560,35 @@
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G239" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H239" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I239" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J239" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N239" s="2"/>
-      <c r="O239" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N239" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O239" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P239" t="s" s="2">
         <v>81</v>
       </c>
@@ -33755,13 +33612,13 @@
         <v>81</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y239" t="s" s="2">
-        <v>81</v>
+        <v>825</v>
       </c>
       <c r="Z239" t="s" s="2">
-        <v>81</v>
+        <v>826</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>81</v>
@@ -33779,19 +33636,19 @@
         <v>81</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>111</v>
+        <v>256</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK239" t="s" s="2">
         <v>81</v>
@@ -33809,7 +33666,7 @@
         <v>81</v>
       </c>
       <c r="AP239" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AQ239" t="s" s="2">
         <v>81</v>
@@ -33820,21 +33677,21 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>81</v>
@@ -33846,17 +33703,15 @@
         <v>81</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N240" s="2"/>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>81</v>
@@ -33893,31 +33748,31 @@
         <v>81</v>
       </c>
       <c r="AB240" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC240" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD240" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE240" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="AK240" t="s" s="2">
         <v>81</v>
@@ -33944,48 +33799,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G241" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H241" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I241" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>252</v>
+        <v>115</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>253</v>
+        <v>116</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>81</v>
       </c>
@@ -34009,31 +33862,31 @@
         <v>81</v>
       </c>
       <c r="X241" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="Y241" t="s" s="2">
-        <v>834</v>
+        <v>81</v>
       </c>
       <c r="Z241" t="s" s="2">
-        <v>835</v>
+        <v>81</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB241" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AC241" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AD241" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE241" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>256</v>
+        <v>121</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>82</v>
@@ -34045,7 +33898,7 @@
         <v>201</v>
       </c>
       <c r="AJ241" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK241" t="s" s="2">
         <v>81</v>
@@ -34063,7 +33916,7 @@
         <v>81</v>
       </c>
       <c r="AP241" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AQ241" t="s" s="2">
         <v>81</v>
@@ -34072,12 +33925,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="242" hidden="true">
+    <row r="242">
       <c r="A242" t="s" s="2">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -34085,31 +33938,35 @@
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G242" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H242" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I242" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J242" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>109</v>
+        <v>264</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N242" s="2"/>
-      <c r="O242" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N242" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O242" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P242" t="s" s="2">
         <v>81</v>
       </c>
@@ -34157,7 +34014,7 @@
         <v>81</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>82</v>
@@ -34166,10 +34023,10 @@
         <v>94</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>81</v>
@@ -34187,7 +34044,7 @@
         <v>81</v>
       </c>
       <c r="AP242" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="AQ242" t="s" s="2">
         <v>81</v>
@@ -34198,21 +34055,21 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>81</v>
@@ -34221,19 +34078,19 @@
         <v>81</v>
       </c>
       <c r="J243" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>115</v>
+        <v>273</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>116</v>
+        <v>274</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>117</v>
+        <v>275</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
@@ -34271,31 +34128,31 @@
         <v>81</v>
       </c>
       <c r="AB243" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC243" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD243" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE243" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>121</v>
+        <v>276</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH243" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI243" t="s" s="2">
         <v>201</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK243" t="s" s="2">
         <v>81</v>
@@ -34313,7 +34170,7 @@
         <v>81</v>
       </c>
       <c r="AP243" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AQ243" t="s" s="2">
         <v>81</v>
@@ -34324,10 +34181,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -34350,19 +34207,19 @@
         <v>95</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>266</v>
+        <v>556</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>81</v>
@@ -34411,7 +34268,7 @@
         <v>81</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>82</v>
@@ -34441,7 +34298,7 @@
         <v>81</v>
       </c>
       <c r="AP244" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AQ244" t="s" s="2">
         <v>81</v>
@@ -34452,10 +34309,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -34481,15 +34338,17 @@
         <v>108</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O245" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="O245" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P245" t="s" s="2">
         <v>81</v>
       </c>
@@ -34537,7 +34396,7 @@
         <v>81</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>82</v>
@@ -34567,7 +34426,7 @@
         <v>81</v>
       </c>
       <c r="AP245" t="s" s="2">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="AQ245" t="s" s="2">
         <v>81</v>
@@ -34576,12 +34435,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -34589,13 +34448,13 @@
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G246" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H246" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I246" t="s" s="2">
         <v>81</v>
@@ -34604,19 +34463,19 @@
         <v>95</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>169</v>
+        <v>296</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>556</v>
+        <v>299</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>81</v>
@@ -34665,7 +34524,7 @@
         <v>81</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>82</v>
@@ -34695,7 +34554,7 @@
         <v>81</v>
       </c>
       <c r="AP246" t="s" s="2">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="AQ246" t="s" s="2">
         <v>81</v>
@@ -34706,10 +34565,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -34735,16 +34594,16 @@
         <v>108</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>556</v>
+        <v>307</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>81</v>
@@ -34793,7 +34652,7 @@
         <v>81</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>82</v>
@@ -34823,7 +34682,7 @@
         <v>81</v>
       </c>
       <c r="AP247" t="s" s="2">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="AQ247" t="s" s="2">
         <v>81</v>
@@ -34834,10 +34693,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -34860,19 +34719,19 @@
         <v>95</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>296</v>
+        <v>845</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>297</v>
+        <v>846</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>298</v>
+        <v>847</v>
       </c>
       <c r="N248" t="s" s="2">
-        <v>299</v>
+        <v>848</v>
       </c>
       <c r="O248" t="s" s="2">
-        <v>300</v>
+        <v>849</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>81</v>
@@ -34921,7 +34780,7 @@
         <v>81</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>301</v>
+        <v>850</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>82</v>
@@ -34930,7 +34789,7 @@
         <v>94</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>106</v>
@@ -34951,7 +34810,7 @@
         <v>81</v>
       </c>
       <c r="AP248" t="s" s="2">
-        <v>302</v>
+        <v>851</v>
       </c>
       <c r="AQ248" t="s" s="2">
         <v>81</v>
@@ -34962,10 +34821,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -34982,30 +34841,30 @@
         <v>81</v>
       </c>
       <c r="I249" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J249" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>305</v>
+        <v>854</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N249" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>855</v>
+      </c>
+      <c r="N249" s="2"/>
       <c r="O249" t="s" s="2">
-        <v>308</v>
+        <v>856</v>
       </c>
       <c r="P249" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q249" s="2"/>
+      <c r="Q249" t="s" s="2">
+        <v>857</v>
+      </c>
       <c r="R249" t="s" s="2">
         <v>81</v>
       </c>
@@ -35025,13 +34884,13 @@
         <v>81</v>
       </c>
       <c r="X249" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y249" t="s" s="2">
-        <v>81</v>
+        <v>858</v>
       </c>
       <c r="Z249" t="s" s="2">
-        <v>81</v>
+        <v>859</v>
       </c>
       <c r="AA249" t="s" s="2">
         <v>81</v>
@@ -35049,7 +34908,7 @@
         <v>81</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>309</v>
+        <v>860</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>82</v>
@@ -35058,7 +34917,7 @@
         <v>94</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>106</v>
@@ -35079,7 +34938,7 @@
         <v>81</v>
       </c>
       <c r="AP249" t="s" s="2">
-        <v>311</v>
+        <v>861</v>
       </c>
       <c r="AQ249" t="s" s="2">
         <v>81</v>
@@ -35090,10 +34949,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -35113,19 +34972,21 @@
         <v>81</v>
       </c>
       <c r="J250" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>231</v>
+        <v>108</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="N250" s="2"/>
-      <c r="O250" s="2"/>
+      <c r="O250" t="s" s="2">
+        <v>866</v>
+      </c>
       <c r="P250" t="s" s="2">
         <v>81</v>
       </c>
@@ -35173,7 +35034,7 @@
         <v>81</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>82</v>
@@ -35185,7 +35046,7 @@
         <v>81</v>
       </c>
       <c r="AJ250" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK250" t="s" s="2">
         <v>81</v>
@@ -35203,7 +35064,7 @@
         <v>81</v>
       </c>
       <c r="AP250" t="s" s="2">
-        <v>81</v>
+        <v>868</v>
       </c>
       <c r="AQ250" t="s" s="2">
         <v>81</v>
@@ -35212,12 +35073,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -35231,7 +35092,7 @@
         <v>94</v>
       </c>
       <c r="H251" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I251" t="s" s="2">
         <v>81</v>
@@ -35240,24 +35101,22 @@
         <v>95</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="N251" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="O251" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="N251" s="2"/>
+      <c r="O251" t="s" s="2">
+        <v>873</v>
+      </c>
       <c r="P251" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q251" t="s" s="2">
-        <v>862</v>
-      </c>
+      <c r="Q251" s="2"/>
       <c r="R251" t="s" s="2">
         <v>81</v>
       </c>
@@ -35301,7 +35160,7 @@
         <v>81</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>82</v>
@@ -35310,7 +35169,7 @@
         <v>94</v>
       </c>
       <c r="AI251" t="s" s="2">
-        <v>806</v>
+        <v>875</v>
       </c>
       <c r="AJ251" t="s" s="2">
         <v>106</v>
@@ -35322,7 +35181,7 @@
         <v>81</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>864</v>
+        <v>81</v>
       </c>
       <c r="AN251" t="s" s="2">
         <v>81</v>
@@ -35331,7 +35190,7 @@
         <v>81</v>
       </c>
       <c r="AP251" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="AQ251" t="s" s="2">
         <v>81</v>
@@ -35342,10 +35201,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -35365,19 +35224,23 @@
         <v>81</v>
       </c>
       <c r="J252" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>811</v>
+        <v>878</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="N252" s="2"/>
-      <c r="O252" s="2"/>
+        <v>879</v>
+      </c>
+      <c r="N252" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="O252" t="s" s="2">
+        <v>881</v>
+      </c>
       <c r="P252" t="s" s="2">
         <v>81</v>
       </c>
@@ -35425,7 +35288,7 @@
         <v>81</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>111</v>
+        <v>882</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>82</v>
@@ -35437,7 +35300,7 @@
         <v>81</v>
       </c>
       <c r="AJ252" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK252" t="s" s="2">
         <v>81</v>
@@ -35455,7 +35318,7 @@
         <v>81</v>
       </c>
       <c r="AP252" t="s" s="2">
-        <v>81</v>
+        <v>868</v>
       </c>
       <c r="AQ252" t="s" s="2">
         <v>81</v>
@@ -35466,10 +35329,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>869</v>
+        <v>883</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -35480,10 +35343,10 @@
         <v>82</v>
       </c>
       <c r="G253" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H253" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I253" t="s" s="2">
         <v>81</v>
@@ -35492,15 +35355,17 @@
         <v>81</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>114</v>
+        <v>782</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>192</v>
+        <v>884</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N253" s="2"/>
+        <v>885</v>
+      </c>
+      <c r="N253" t="s" s="2">
+        <v>886</v>
+      </c>
       <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
         <v>81</v>
@@ -35537,7 +35402,7 @@
         <v>81</v>
       </c>
       <c r="AB253" t="s" s="2">
-        <v>118</v>
+        <v>325</v>
       </c>
       <c r="AC253" s="2"/>
       <c r="AD253" t="s" s="2">
@@ -35547,19 +35412,19 @@
         <v>120</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>121</v>
+        <v>883</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH253" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI253" t="s" s="2">
-        <v>81</v>
+        <v>887</v>
       </c>
       <c r="AJ253" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK253" t="s" s="2">
         <v>81</v>
@@ -35568,7 +35433,7 @@
         <v>81</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>81</v>
+        <v>786</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>81</v>
@@ -35580,7 +35445,7 @@
         <v>81</v>
       </c>
       <c r="AQ253" t="s" s="2">
-        <v>81</v>
+        <v>888</v>
       </c>
       <c r="AR253" t="s" s="2">
         <v>81</v>
@@ -35588,13 +35453,13 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>869</v>
+        <v>883</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>871</v>
+        <v>890</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>81</v>
@@ -35616,15 +35481,17 @@
         <v>81</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>817</v>
+        <v>231</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>534</v>
+        <v>891</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N254" s="2"/>
+        <v>892</v>
+      </c>
+      <c r="N254" t="s" s="2">
+        <v>886</v>
+      </c>
       <c r="O254" s="2"/>
       <c r="P254" t="s" s="2">
         <v>81</v>
@@ -35673,19 +35540,19 @@
         <v>81</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>121</v>
+        <v>883</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>201</v>
+        <v>887</v>
       </c>
       <c r="AJ254" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK254" t="s" s="2">
         <v>81</v>
@@ -35694,7 +35561,7 @@
         <v>81</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>81</v>
+        <v>893</v>
       </c>
       <c r="AN254" t="s" s="2">
         <v>81</v>
@@ -35706,20 +35573,22 @@
         <v>81</v>
       </c>
       <c r="AQ254" t="s" s="2">
-        <v>81</v>
+        <v>888</v>
       </c>
       <c r="AR254" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="255" hidden="true">
+    <row r="255">
       <c r="A255" t="s" s="2">
-        <v>872</v>
+        <v>894</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="C255" s="2"/>
+        <v>883</v>
+      </c>
+      <c r="C255" t="s" s="2">
+        <v>895</v>
+      </c>
       <c r="D255" t="s" s="2">
         <v>81</v>
       </c>
@@ -35731,7 +35600,7 @@
         <v>94</v>
       </c>
       <c r="H255" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I255" t="s" s="2">
         <v>81</v>
@@ -35740,15 +35609,17 @@
         <v>81</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>108</v>
+        <v>797</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>109</v>
+        <v>896</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N255" s="2"/>
+        <v>897</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>886</v>
+      </c>
       <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
         <v>81</v>
@@ -35797,7 +35668,7 @@
         <v>81</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>111</v>
+        <v>883</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>82</v>
@@ -35806,10 +35677,10 @@
         <v>94</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>81</v>
+        <v>887</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK255" t="s" s="2">
         <v>81</v>
@@ -35830,7 +35701,7 @@
         <v>81</v>
       </c>
       <c r="AQ255" t="s" s="2">
-        <v>81</v>
+        <v>888</v>
       </c>
       <c r="AR255" t="s" s="2">
         <v>81</v>
@@ -35838,21 +35709,21 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>874</v>
+        <v>898</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>875</v>
+        <v>899</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>81</v>
@@ -35864,17 +35735,15 @@
         <v>81</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N256" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N256" s="2"/>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
         <v>81</v>
@@ -35911,31 +35780,31 @@
         <v>81</v>
       </c>
       <c r="AB256" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC256" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD256" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE256" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>81</v>
@@ -35962,26 +35831,26 @@
         <v>81</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>877</v>
+        <v>901</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H257" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I257" t="s" s="2">
         <v>81</v>
@@ -35990,16 +35859,16 @@
         <v>81</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>209</v>
+        <v>116</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
@@ -36007,7 +35876,7 @@
       </c>
       <c r="Q257" s="2"/>
       <c r="R257" t="s" s="2">
-        <v>824</v>
+        <v>81</v>
       </c>
       <c r="S257" t="s" s="2">
         <v>81</v>
@@ -36037,31 +35906,31 @@
         <v>81</v>
       </c>
       <c r="AB257" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AC257" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AD257" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE257" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="AG257" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI257" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="AK257" t="s" s="2">
         <v>81</v>
@@ -36088,26 +35957,28 @@
         <v>81</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>878</v>
+        <v>902</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="C258" s="2"/>
+        <v>901</v>
+      </c>
+      <c r="C258" t="s" s="2">
+        <v>903</v>
+      </c>
       <c r="D258" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G258" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H258" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I258" t="s" s="2">
         <v>81</v>
@@ -36116,15 +35987,17 @@
         <v>81</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>243</v>
+        <v>806</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>216</v>
+        <v>904</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N258" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="N258" t="s" s="2">
+        <v>808</v>
+      </c>
       <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>81</v>
@@ -36173,19 +36046,19 @@
         <v>81</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>218</v>
+        <v>121</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH258" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI258" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ258" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK258" t="s" s="2">
         <v>81</v>
@@ -36194,7 +36067,7 @@
         <v>81</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>880</v>
+        <v>81</v>
       </c>
       <c r="AN258" t="s" s="2">
         <v>81</v>
@@ -36214,10 +36087,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -36338,10 +36211,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>883</v>
+        <v>907</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>884</v>
+        <v>908</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -36352,7 +36225,7 @@
         <v>82</v>
       </c>
       <c r="G260" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H260" t="s" s="2">
         <v>81</v>
@@ -36464,10 +36337,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>885</v>
+        <v>909</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>886</v>
+        <v>910</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -36487,29 +36360,27 @@
         <v>81</v>
       </c>
       <c r="J261" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="N261" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O261" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="O261" s="2"/>
       <c r="P261" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q261" s="2"/>
       <c r="R261" t="s" s="2">
-        <v>81</v>
+        <v>815</v>
       </c>
       <c r="S261" t="s" s="2">
         <v>81</v>
@@ -36527,13 +36398,13 @@
         <v>81</v>
       </c>
       <c r="X261" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="Y261" t="s" s="2">
-        <v>834</v>
+        <v>81</v>
       </c>
       <c r="Z261" t="s" s="2">
-        <v>835</v>
+        <v>81</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>81</v>
@@ -36551,19 +36422,19 @@
         <v>81</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="AG261" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH261" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI261" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ261" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK261" t="s" s="2">
         <v>81</v>
@@ -36581,7 +36452,7 @@
         <v>81</v>
       </c>
       <c r="AP261" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AQ261" t="s" s="2">
         <v>81</v>
@@ -36590,12 +36461,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="262" hidden="true">
+    <row r="262">
       <c r="A262" t="s" s="2">
-        <v>887</v>
+        <v>911</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -36603,13 +36474,13 @@
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G262" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H262" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I262" t="s" s="2">
         <v>81</v>
@@ -36618,13 +36489,13 @@
         <v>81</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>108</v>
+        <v>243</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="2"/>
@@ -36675,7 +36546,7 @@
         <v>81</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>111</v>
+        <v>218</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>82</v>
@@ -36684,10 +36555,10 @@
         <v>94</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AJ262" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK262" t="s" s="2">
         <v>81</v>
@@ -36696,7 +36567,7 @@
         <v>81</v>
       </c>
       <c r="AM262" t="s" s="2">
-        <v>81</v>
+        <v>913</v>
       </c>
       <c r="AN262" t="s" s="2">
         <v>81</v>
@@ -36716,21 +36587,21 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>889</v>
+        <v>914</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>890</v>
+        <v>915</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E263" s="2"/>
       <c r="F263" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H263" t="s" s="2">
         <v>81</v>
@@ -36742,17 +36613,15 @@
         <v>81</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N263" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N263" s="2"/>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
         <v>81</v>
@@ -36789,31 +36658,31 @@
         <v>81</v>
       </c>
       <c r="AB263" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC263" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD263" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE263" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH263" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ263" t="s" s="2">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="AK263" t="s" s="2">
         <v>81</v>
@@ -36840,48 +36709,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>891</v>
+        <v>916</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>892</v>
+        <v>917</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E264" s="2"/>
       <c r="F264" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G264" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H264" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I264" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J264" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>264</v>
+        <v>115</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="N264" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O264" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
         <v>81</v>
       </c>
@@ -36917,31 +36784,31 @@
         <v>81</v>
       </c>
       <c r="AB264" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AC264" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AD264" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE264" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>269</v>
+        <v>121</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH264" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI264" t="s" s="2">
         <v>201</v>
       </c>
       <c r="AJ264" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK264" t="s" s="2">
         <v>81</v>
@@ -36959,7 +36826,7 @@
         <v>81</v>
       </c>
       <c r="AP264" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="AQ264" t="s" s="2">
         <v>81</v>
@@ -36968,12 +36835,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="265" hidden="true">
+    <row r="265">
       <c r="A265" t="s" s="2">
-        <v>893</v>
+        <v>918</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>894</v>
+        <v>919</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -36981,13 +36848,13 @@
       </c>
       <c r="E265" s="2"/>
       <c r="F265" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G265" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H265" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I265" t="s" s="2">
         <v>81</v>
@@ -36996,18 +36863,20 @@
         <v>95</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O265" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O265" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P265" t="s" s="2">
         <v>81</v>
       </c>
@@ -37031,13 +36900,13 @@
         <v>81</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>81</v>
+        <v>825</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>81</v>
+        <v>826</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>81</v>
@@ -37055,13 +36924,13 @@
         <v>81</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH265" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI265" t="s" s="2">
         <v>201</v>
@@ -37085,7 +36954,7 @@
         <v>81</v>
       </c>
       <c r="AP265" t="s" s="2">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="AQ265" t="s" s="2">
         <v>81</v>
@@ -37094,12 +36963,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>895</v>
+        <v>920</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>896</v>
+        <v>921</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -37107,35 +36976,31 @@
       </c>
       <c r="E266" s="2"/>
       <c r="F266" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G266" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H266" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I266" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J266" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>281</v>
+        <v>109</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N266" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O266" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N266" s="2"/>
+      <c r="O266" s="2"/>
       <c r="P266" t="s" s="2">
         <v>81</v>
       </c>
@@ -37183,7 +37048,7 @@
         <v>81</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>82</v>
@@ -37192,10 +37057,10 @@
         <v>94</v>
       </c>
       <c r="AI266" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ266" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK266" t="s" s="2">
         <v>81</v>
@@ -37213,7 +37078,7 @@
         <v>81</v>
       </c>
       <c r="AP266" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
       <c r="AQ266" t="s" s="2">
         <v>81</v>
@@ -37224,21 +37089,21 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>897</v>
+        <v>922</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>898</v>
+        <v>923</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G267" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H267" t="s" s="2">
         <v>81</v>
@@ -37247,23 +37112,21 @@
         <v>81</v>
       </c>
       <c r="J267" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>289</v>
+        <v>115</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>290</v>
+        <v>116</v>
       </c>
       <c r="N267" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O267" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
         <v>81</v>
       </c>
@@ -37299,31 +37162,31 @@
         <v>81</v>
       </c>
       <c r="AB267" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AC267" t="s" s="2">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AD267" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE267" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>292</v>
+        <v>121</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH267" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI267" t="s" s="2">
         <v>201</v>
       </c>
       <c r="AJ267" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK267" t="s" s="2">
         <v>81</v>
@@ -37341,7 +37204,7 @@
         <v>81</v>
       </c>
       <c r="AP267" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="AQ267" t="s" s="2">
         <v>81</v>
@@ -37350,12 +37213,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="268" hidden="true">
+    <row r="268">
       <c r="A268" t="s" s="2">
-        <v>899</v>
+        <v>924</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -37363,13 +37226,13 @@
       </c>
       <c r="E268" s="2"/>
       <c r="F268" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G268" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H268" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I268" t="s" s="2">
         <v>81</v>
@@ -37378,19 +37241,19 @@
         <v>95</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>296</v>
+        <v>135</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="O268" t="s" s="2">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>81</v>
@@ -37439,7 +37302,7 @@
         <v>81</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>82</v>
@@ -37469,7 +37332,7 @@
         <v>81</v>
       </c>
       <c r="AP268" t="s" s="2">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="AQ268" t="s" s="2">
         <v>81</v>
@@ -37480,10 +37343,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>901</v>
+        <v>926</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>902</v>
+        <v>927</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -37509,17 +37372,15 @@
         <v>108</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O269" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O269" s="2"/>
       <c r="P269" t="s" s="2">
         <v>81</v>
       </c>
@@ -37567,7 +37428,7 @@
         <v>81</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>82</v>
@@ -37597,7 +37458,7 @@
         <v>81</v>
       </c>
       <c r="AP269" t="s" s="2">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="AQ269" t="s" s="2">
         <v>81</v>
@@ -37606,12 +37467,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="270" hidden="true">
+    <row r="270">
       <c r="A270" t="s" s="2">
-        <v>903</v>
+        <v>928</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>904</v>
+        <v>929</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -37619,31 +37480,35 @@
       </c>
       <c r="E270" s="2"/>
       <c r="F270" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G270" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H270" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I270" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J270" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>231</v>
+        <v>169</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>854</v>
+        <v>281</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="N270" s="2"/>
-      <c r="O270" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N270" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P270" t="s" s="2">
         <v>81</v>
       </c>
@@ -37691,7 +37556,7 @@
         <v>81</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>856</v>
+        <v>284</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>82</v>
@@ -37700,10 +37565,10 @@
         <v>94</v>
       </c>
       <c r="AI270" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AJ270" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK270" t="s" s="2">
         <v>81</v>
@@ -37721,7 +37586,7 @@
         <v>81</v>
       </c>
       <c r="AP270" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="AQ270" t="s" s="2">
         <v>81</v>
@@ -37730,16 +37595,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>905</v>
+        <v>930</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C271" t="s" s="2">
-        <v>906</v>
-      </c>
+        <v>931</v>
+      </c>
+      <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
         <v>81</v>
       </c>
@@ -37751,7 +37614,7 @@
         <v>94</v>
       </c>
       <c r="H271" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I271" t="s" s="2">
         <v>81</v>
@@ -37760,18 +37623,20 @@
         <v>95</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>231</v>
+        <v>108</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>907</v>
+        <v>289</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>908</v>
+        <v>290</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O271" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="O271" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P271" t="s" s="2">
         <v>81</v>
       </c>
@@ -37819,7 +37684,7 @@
         <v>81</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>781</v>
+        <v>292</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>82</v>
@@ -37828,7 +37693,7 @@
         <v>94</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AJ271" t="s" s="2">
         <v>106</v>
@@ -37843,31 +37708,29 @@
         <v>81</v>
       </c>
       <c r="AN271" t="s" s="2">
-        <v>788</v>
+        <v>81</v>
       </c>
       <c r="AO271" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP271" t="s" s="2">
-        <v>789</v>
+        <v>293</v>
       </c>
       <c r="AQ271" t="s" s="2">
-        <v>790</v>
+        <v>81</v>
       </c>
       <c r="AR271" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>909</v>
+        <v>932</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C272" t="s" s="2">
-        <v>910</v>
-      </c>
+        <v>933</v>
+      </c>
+      <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
         <v>81</v>
       </c>
@@ -37879,7 +37742,7 @@
         <v>94</v>
       </c>
       <c r="H272" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I272" t="s" s="2">
         <v>81</v>
@@ -37888,18 +37751,20 @@
         <v>95</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>911</v>
+        <v>296</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>912</v>
+        <v>297</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>913</v>
+        <v>298</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O272" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O272" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P272" t="s" s="2">
         <v>81</v>
       </c>
@@ -37947,7 +37812,7 @@
         <v>81</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>781</v>
+        <v>301</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>82</v>
@@ -37956,7 +37821,7 @@
         <v>94</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AJ272" t="s" s="2">
         <v>106</v>
@@ -37971,16 +37836,16 @@
         <v>81</v>
       </c>
       <c r="AN272" t="s" s="2">
-        <v>788</v>
+        <v>81</v>
       </c>
       <c r="AO272" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP272" t="s" s="2">
-        <v>789</v>
+        <v>302</v>
       </c>
       <c r="AQ272" t="s" s="2">
-        <v>790</v>
+        <v>81</v>
       </c>
       <c r="AR272" t="s" s="2">
         <v>81</v>
@@ -37988,10 +37853,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>797</v>
+        <v>935</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -38011,19 +37876,23 @@
         <v>81</v>
       </c>
       <c r="J273" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K273" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>109</v>
+        <v>305</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N273" s="2"/>
-      <c r="O273" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N273" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O273" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P273" t="s" s="2">
         <v>81</v>
       </c>
@@ -38071,7 +37940,7 @@
         <v>81</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>111</v>
+        <v>309</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>82</v>
@@ -38080,10 +37949,10 @@
         <v>94</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK273" t="s" s="2">
         <v>81</v>
@@ -38101,7 +37970,7 @@
         <v>81</v>
       </c>
       <c r="AP273" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AQ273" t="s" s="2">
         <v>81</v>
@@ -38112,21 +37981,21 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>915</v>
+        <v>936</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>799</v>
+        <v>937</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G274" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H274" t="s" s="2">
         <v>81</v>
@@ -38135,21 +38004,23 @@
         <v>81</v>
       </c>
       <c r="J274" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>114</v>
+        <v>845</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>115</v>
+        <v>846</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>116</v>
+        <v>847</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O274" s="2"/>
+        <v>848</v>
+      </c>
+      <c r="O274" t="s" s="2">
+        <v>849</v>
+      </c>
       <c r="P274" t="s" s="2">
         <v>81</v>
       </c>
@@ -38185,31 +38056,31 @@
         <v>81</v>
       </c>
       <c r="AB274" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC274" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD274" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE274" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>121</v>
+        <v>850</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH274" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI274" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK274" t="s" s="2">
         <v>81</v>
@@ -38227,7 +38098,7 @@
         <v>81</v>
       </c>
       <c r="AP274" t="s" s="2">
-        <v>81</v>
+        <v>851</v>
       </c>
       <c r="AQ274" t="s" s="2">
         <v>81</v>
@@ -38238,14 +38109,12 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>916</v>
+        <v>938</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="C275" t="s" s="2">
-        <v>917</v>
-      </c>
+        <v>939</v>
+      </c>
+      <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
         <v>81</v>
       </c>
@@ -38260,28 +38129,30 @@
         <v>81</v>
       </c>
       <c r="I275" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J275" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>817</v>
+        <v>169</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>918</v>
+        <v>854</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N275" t="s" s="2">
-        <v>919</v>
-      </c>
-      <c r="O275" s="2"/>
+        <v>855</v>
+      </c>
+      <c r="N275" s="2"/>
+      <c r="O275" t="s" s="2">
+        <v>856</v>
+      </c>
       <c r="P275" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q275" s="2"/>
+      <c r="Q275" t="s" s="2">
+        <v>857</v>
+      </c>
       <c r="R275" t="s" s="2">
         <v>81</v>
       </c>
@@ -38301,13 +38172,13 @@
         <v>81</v>
       </c>
       <c r="X275" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="Y275" t="s" s="2">
-        <v>81</v>
+        <v>858</v>
       </c>
       <c r="Z275" t="s" s="2">
-        <v>81</v>
+        <v>859</v>
       </c>
       <c r="AA275" t="s" s="2">
         <v>81</v>
@@ -38325,19 +38196,19 @@
         <v>81</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>121</v>
+        <v>860</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH275" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI275" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ275" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK275" t="s" s="2">
         <v>81</v>
@@ -38355,7 +38226,7 @@
         <v>81</v>
       </c>
       <c r="AP275" t="s" s="2">
-        <v>81</v>
+        <v>861</v>
       </c>
       <c r="AQ275" t="s" s="2">
         <v>81</v>
@@ -38366,10 +38237,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -38389,19 +38260,21 @@
         <v>81</v>
       </c>
       <c r="J276" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K276" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>109</v>
+        <v>864</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>110</v>
+        <v>865</v>
       </c>
       <c r="N276" s="2"/>
-      <c r="O276" s="2"/>
+      <c r="O276" t="s" s="2">
+        <v>866</v>
+      </c>
       <c r="P276" t="s" s="2">
         <v>81</v>
       </c>
@@ -38449,7 +38322,7 @@
         <v>81</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>111</v>
+        <v>867</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>82</v>
@@ -38461,7 +38334,7 @@
         <v>81</v>
       </c>
       <c r="AJ276" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK276" t="s" s="2">
         <v>81</v>
@@ -38479,7 +38352,7 @@
         <v>81</v>
       </c>
       <c r="AP276" t="s" s="2">
-        <v>81</v>
+        <v>868</v>
       </c>
       <c r="AQ276" t="s" s="2">
         <v>81</v>
@@ -38490,21 +38363,21 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>922</v>
+        <v>942</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E277" s="2"/>
       <c r="F277" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G277" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H277" t="s" s="2">
         <v>81</v>
@@ -38513,21 +38386,21 @@
         <v>81</v>
       </c>
       <c r="J277" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>115</v>
+        <v>871</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N277" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O277" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="N277" s="2"/>
+      <c r="O277" t="s" s="2">
+        <v>873</v>
+      </c>
       <c r="P277" t="s" s="2">
         <v>81</v>
       </c>
@@ -38563,31 +38436,31 @@
         <v>81</v>
       </c>
       <c r="AB277" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC277" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD277" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE277" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>121</v>
+        <v>874</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH277" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI277" t="s" s="2">
-        <v>201</v>
+        <v>875</v>
       </c>
       <c r="AJ277" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK277" t="s" s="2">
         <v>81</v>
@@ -38605,7 +38478,7 @@
         <v>81</v>
       </c>
       <c r="AP277" t="s" s="2">
-        <v>81</v>
+        <v>868</v>
       </c>
       <c r="AQ277" t="s" s="2">
         <v>81</v>
@@ -38614,12 +38487,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>925</v>
+        <v>945</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -38627,39 +38500,41 @@
       </c>
       <c r="E278" s="2"/>
       <c r="F278" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G278" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H278" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I278" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J278" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I278" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J278" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K278" t="s" s="2">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>208</v>
+        <v>878</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>209</v>
+        <v>879</v>
       </c>
       <c r="N278" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O278" s="2"/>
+        <v>880</v>
+      </c>
+      <c r="O278" t="s" s="2">
+        <v>881</v>
+      </c>
       <c r="P278" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q278" s="2"/>
       <c r="R278" t="s" s="2">
-        <v>824</v>
+        <v>81</v>
       </c>
       <c r="S278" t="s" s="2">
         <v>81</v>
@@ -38701,10 +38576,10 @@
         <v>81</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>212</v>
+        <v>882</v>
       </c>
       <c r="AG278" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH278" t="s" s="2">
         <v>94</v>
@@ -38713,7 +38588,7 @@
         <v>81</v>
       </c>
       <c r="AJ278" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK278" t="s" s="2">
         <v>81</v>
@@ -38731,7 +38606,7 @@
         <v>81</v>
       </c>
       <c r="AP278" t="s" s="2">
-        <v>81</v>
+        <v>868</v>
       </c>
       <c r="AQ278" t="s" s="2">
         <v>81</v>
@@ -38742,10 +38617,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>926</v>
+        <v>946</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>927</v>
+        <v>946</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -38765,16 +38640,16 @@
         <v>81</v>
       </c>
       <c r="J279" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>216</v>
+        <v>947</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>217</v>
+        <v>948</v>
       </c>
       <c r="N279" s="2"/>
       <c r="O279" s="2"/>
@@ -38825,7 +38700,7 @@
         <v>81</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>218</v>
+        <v>946</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>82</v>
@@ -38834,7 +38709,7 @@
         <v>94</v>
       </c>
       <c r="AI279" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ279" t="s" s="2">
         <v>106</v>
@@ -38846,7 +38721,7 @@
         <v>81</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>81</v>
+        <v>949</v>
       </c>
       <c r="AN279" t="s" s="2">
         <v>81</v>
@@ -38855,10 +38730,10 @@
         <v>81</v>
       </c>
       <c r="AP279" t="s" s="2">
-        <v>81</v>
+        <v>950</v>
       </c>
       <c r="AQ279" t="s" s="2">
-        <v>81</v>
+        <v>951</v>
       </c>
       <c r="AR279" t="s" s="2">
         <v>81</v>
@@ -38866,10 +38741,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>928</v>
+        <v>952</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>929</v>
+        <v>952</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -38889,16 +38764,16 @@
         <v>81</v>
       </c>
       <c r="J280" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>108</v>
+        <v>953</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>109</v>
+        <v>954</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>110</v>
+        <v>955</v>
       </c>
       <c r="N280" s="2"/>
       <c r="O280" s="2"/>
@@ -38949,7 +38824,7 @@
         <v>81</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>111</v>
+        <v>952</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>82</v>
@@ -38961,7 +38836,7 @@
         <v>81</v>
       </c>
       <c r="AJ280" t="s" s="2">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AK280" t="s" s="2">
         <v>81</v>
@@ -38982,7 +38857,7 @@
         <v>81</v>
       </c>
       <c r="AQ280" t="s" s="2">
-        <v>81</v>
+        <v>956</v>
       </c>
       <c r="AR280" t="s" s="2">
         <v>81</v>
@@ -38990,21 +38865,21 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>931</v>
+        <v>957</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="E281" s="2"/>
       <c r="F281" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G281" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H281" t="s" s="2">
         <v>81</v>
@@ -39013,20 +38888,18 @@
         <v>81</v>
       </c>
       <c r="J281" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>114</v>
+        <v>953</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>115</v>
+        <v>958</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N281" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="N281" s="2"/>
       <c r="O281" s="2"/>
       <c r="P281" t="s" s="2">
         <v>81</v>
@@ -39063,31 +38936,31 @@
         <v>81</v>
       </c>
       <c r="AB281" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC281" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD281" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE281" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>121</v>
+        <v>957</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH281" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ281" t="s" s="2">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="AK281" t="s" s="2">
         <v>81</v>
@@ -39105,21 +38978,21 @@
         <v>81</v>
       </c>
       <c r="AP281" t="s" s="2">
-        <v>81</v>
+        <v>960</v>
       </c>
       <c r="AQ281" t="s" s="2">
-        <v>81</v>
+        <v>961</v>
       </c>
       <c r="AR281" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>932</v>
+        <v>962</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>933</v>
+        <v>962</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -39127,35 +39000,31 @@
       </c>
       <c r="E282" s="2"/>
       <c r="F282" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G282" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H282" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I282" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J282" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>147</v>
+        <v>963</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>252</v>
+        <v>964</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N282" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O282" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>965</v>
+      </c>
+      <c r="N282" s="2"/>
+      <c r="O282" s="2"/>
       <c r="P282" t="s" s="2">
         <v>81</v>
       </c>
@@ -39179,13 +39048,13 @@
         <v>81</v>
       </c>
       <c r="X282" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="Y282" t="s" s="2">
-        <v>834</v>
+        <v>81</v>
       </c>
       <c r="Z282" t="s" s="2">
-        <v>835</v>
+        <v>81</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>81</v>
@@ -39203,7 +39072,7 @@
         <v>81</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>256</v>
+        <v>962</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>82</v>
@@ -39212,10 +39081,10 @@
         <v>83</v>
       </c>
       <c r="AI282" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ282" t="s" s="2">
-        <v>106</v>
+        <v>966</v>
       </c>
       <c r="AK282" t="s" s="2">
         <v>81</v>
@@ -39233,7 +39102,7 @@
         <v>81</v>
       </c>
       <c r="AP282" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AQ282" t="s" s="2">
         <v>81</v>
@@ -39244,10 +39113,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>934</v>
+        <v>967</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>935</v>
+        <v>967</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -39368,10 +39237,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>936</v>
+        <v>968</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>937</v>
+        <v>968</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -39441,16 +39310,16 @@
         <v>81</v>
       </c>
       <c r="AB284" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AC284" t="s" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="AD284" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE284" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AF284" t="s" s="2">
         <v>121</v>
@@ -39462,7 +39331,7 @@
         <v>83</v>
       </c>
       <c r="AI284" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ284" t="s" s="2">
         <v>122</v>
@@ -39492,47 +39361,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>938</v>
+        <v>969</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>939</v>
+        <v>969</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>81</v>
+        <v>970</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G285" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H285" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I285" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I285" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J285" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>264</v>
+        <v>971</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>265</v>
+        <v>972</v>
       </c>
       <c r="N285" t="s" s="2">
-        <v>266</v>
+        <v>117</v>
       </c>
       <c r="O285" t="s" s="2">
-        <v>267</v>
+        <v>353</v>
       </c>
       <c r="P285" t="s" s="2">
         <v>81</v>
@@ -39581,19 +39450,19 @@
         <v>81</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>269</v>
+        <v>973</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH285" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI285" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ285" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK285" t="s" s="2">
         <v>81</v>
@@ -39611,7 +39480,7 @@
         <v>81</v>
       </c>
       <c r="AP285" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="AQ285" t="s" s="2">
         <v>81</v>
@@ -39622,10 +39491,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>940</v>
+        <v>974</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>941</v>
+        <v>974</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -39645,20 +39514,18 @@
         <v>81</v>
       </c>
       <c r="J286" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>108</v>
+        <v>243</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>273</v>
+        <v>975</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N286" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>976</v>
+      </c>
+      <c r="N286" s="2"/>
       <c r="O286" s="2"/>
       <c r="P286" t="s" s="2">
         <v>81</v>
@@ -39683,13 +39550,13 @@
         <v>81</v>
       </c>
       <c r="X286" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="Y286" t="s" s="2">
-        <v>81</v>
+        <v>977</v>
       </c>
       <c r="Z286" t="s" s="2">
-        <v>81</v>
+        <v>978</v>
       </c>
       <c r="AA286" t="s" s="2">
         <v>81</v>
@@ -39707,7 +39574,7 @@
         <v>81</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>276</v>
+        <v>974</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>82</v>
@@ -39716,7 +39583,7 @@
         <v>94</v>
       </c>
       <c r="AI286" t="s" s="2">
-        <v>201</v>
+        <v>979</v>
       </c>
       <c r="AJ286" t="s" s="2">
         <v>106</v>
@@ -39734,10 +39601,10 @@
         <v>81</v>
       </c>
       <c r="AO286" t="s" s="2">
-        <v>81</v>
+        <v>980</v>
       </c>
       <c r="AP286" t="s" s="2">
-        <v>278</v>
+        <v>421</v>
       </c>
       <c r="AQ286" t="s" s="2">
         <v>81</v>
@@ -39746,12 +39613,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>942</v>
+        <v>981</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>943</v>
+        <v>981</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -39759,35 +39626,31 @@
       </c>
       <c r="E287" s="2"/>
       <c r="F287" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G287" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H287" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I287" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J287" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>169</v>
+        <v>982</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>281</v>
+        <v>983</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N287" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O287" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>984</v>
+      </c>
+      <c r="N287" s="2"/>
+      <c r="O287" s="2"/>
       <c r="P287" t="s" s="2">
         <v>81</v>
       </c>
@@ -39835,16 +39698,16 @@
         <v>81</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>284</v>
+        <v>981</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH287" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI287" t="s" s="2">
-        <v>201</v>
+        <v>979</v>
       </c>
       <c r="AJ287" t="s" s="2">
         <v>106</v>
@@ -39865,7 +39728,7 @@
         <v>81</v>
       </c>
       <c r="AP287" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
       <c r="AQ287" t="s" s="2">
         <v>81</v>
@@ -39876,10 +39739,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>944</v>
+        <v>985</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>945</v>
+        <v>985</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -39899,23 +39762,19 @@
         <v>81</v>
       </c>
       <c r="J288" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>108</v>
+        <v>243</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>289</v>
+        <v>986</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N288" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O288" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="N288" s="2"/>
+      <c r="O288" s="2"/>
       <c r="P288" t="s" s="2">
         <v>81</v>
       </c>
@@ -39939,13 +39798,13 @@
         <v>81</v>
       </c>
       <c r="X288" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="Y288" t="s" s="2">
-        <v>81</v>
+        <v>988</v>
       </c>
       <c r="Z288" t="s" s="2">
-        <v>81</v>
+        <v>989</v>
       </c>
       <c r="AA288" t="s" s="2">
         <v>81</v>
@@ -39963,7 +39822,7 @@
         <v>81</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>82</v>
@@ -39972,7 +39831,7 @@
         <v>94</v>
       </c>
       <c r="AI288" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ288" t="s" s="2">
         <v>106</v>
@@ -39993,7 +39852,7 @@
         <v>81</v>
       </c>
       <c r="AP288" t="s" s="2">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="AQ288" t="s" s="2">
         <v>81</v>
@@ -40002,12 +39861,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="289" hidden="true">
+    <row r="289">
       <c r="A289" t="s" s="2">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>947</v>
+        <v>990</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -40021,29 +39880,27 @@
         <v>94</v>
       </c>
       <c r="H289" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I289" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J289" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>296</v>
+        <v>963</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>297</v>
+        <v>991</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>298</v>
+        <v>992</v>
       </c>
       <c r="N289" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O289" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>993</v>
+      </c>
+      <c r="O289" s="2"/>
       <c r="P289" t="s" s="2">
         <v>81</v>
       </c>
@@ -40091,19 +39948,19 @@
         <v>81</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>301</v>
+        <v>990</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH289" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI289" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ289" t="s" s="2">
-        <v>106</v>
+        <v>994</v>
       </c>
       <c r="AK289" t="s" s="2">
         <v>81</v>
@@ -40121,7 +39978,7 @@
         <v>81</v>
       </c>
       <c r="AP289" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AQ289" t="s" s="2">
         <v>81</v>
@@ -40132,10 +39989,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>949</v>
+        <v>995</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -40155,23 +40012,19 @@
         <v>81</v>
       </c>
       <c r="J290" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K290" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>305</v>
+        <v>109</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N290" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O290" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N290" s="2"/>
+      <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
         <v>81</v>
       </c>
@@ -40219,7 +40072,7 @@
         <v>81</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>309</v>
+        <v>111</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>82</v>
@@ -40228,10 +40081,10 @@
         <v>94</v>
       </c>
       <c r="AI290" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AJ290" t="s" s="2">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="AK290" t="s" s="2">
         <v>81</v>
@@ -40249,7 +40102,7 @@
         <v>81</v>
       </c>
       <c r="AP290" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="AQ290" t="s" s="2">
         <v>81</v>
@@ -40260,21 +40113,21 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>950</v>
+        <v>996</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>951</v>
+        <v>996</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G291" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H291" t="s" s="2">
         <v>81</v>
@@ -40283,23 +40136,21 @@
         <v>81</v>
       </c>
       <c r="J291" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K291" t="s" s="2">
-        <v>952</v>
+        <v>114</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>953</v>
+        <v>115</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>954</v>
+        <v>116</v>
       </c>
       <c r="N291" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="O291" t="s" s="2">
-        <v>956</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O291" s="2"/>
       <c r="P291" t="s" s="2">
         <v>81</v>
       </c>
@@ -40347,19 +40198,19 @@
         <v>81</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>957</v>
+        <v>121</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH291" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI291" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ291" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK291" t="s" s="2">
         <v>81</v>
@@ -40377,7 +40228,7 @@
         <v>81</v>
       </c>
       <c r="AP291" t="s" s="2">
-        <v>958</v>
+        <v>81</v>
       </c>
       <c r="AQ291" t="s" s="2">
         <v>81</v>
@@ -40388,21 +40239,21 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>959</v>
+        <v>997</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>960</v>
+        <v>997</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
-        <v>81</v>
+        <v>970</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G292" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H292" t="s" s="2">
         <v>81</v>
@@ -40414,24 +40265,24 @@
         <v>95</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>962</v>
-      </c>
-      <c r="N292" s="2"/>
+        <v>972</v>
+      </c>
+      <c r="N292" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O292" t="s" s="2">
-        <v>963</v>
+        <v>353</v>
       </c>
       <c r="P292" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q292" t="s" s="2">
-        <v>964</v>
-      </c>
+      <c r="Q292" s="2"/>
       <c r="R292" t="s" s="2">
         <v>81</v>
       </c>
@@ -40451,13 +40302,13 @@
         <v>81</v>
       </c>
       <c r="X292" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="Y292" t="s" s="2">
-        <v>965</v>
+        <v>81</v>
       </c>
       <c r="Z292" t="s" s="2">
-        <v>966</v>
+        <v>81</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>81</v>
@@ -40475,19 +40326,19 @@
         <v>81</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH292" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI292" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ292" t="s" s="2">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="AK292" t="s" s="2">
         <v>81</v>
@@ -40505,7 +40356,7 @@
         <v>81</v>
       </c>
       <c r="AP292" t="s" s="2">
-        <v>968</v>
+        <v>81</v>
       </c>
       <c r="AQ292" t="s" s="2">
         <v>81</v>
@@ -40516,10 +40367,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>969</v>
+        <v>998</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>970</v>
+        <v>998</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -40530,7 +40381,7 @@
         <v>82</v>
       </c>
       <c r="G293" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H293" t="s" s="2">
         <v>81</v>
@@ -40542,18 +40393,16 @@
         <v>95</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>108</v>
+        <v>243</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>971</v>
+        <v>999</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>972</v>
+        <v>1000</v>
       </c>
       <c r="N293" s="2"/>
-      <c r="O293" t="s" s="2">
-        <v>973</v>
-      </c>
+      <c r="O293" s="2"/>
       <c r="P293" t="s" s="2">
         <v>81</v>
       </c>
@@ -40577,13 +40426,13 @@
         <v>81</v>
       </c>
       <c r="X293" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="Y293" t="s" s="2">
-        <v>81</v>
+        <v>1001</v>
       </c>
       <c r="Z293" t="s" s="2">
-        <v>81</v>
+        <v>1002</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>81</v>
@@ -40601,16 +40450,16 @@
         <v>81</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH293" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>81</v>
+        <v>1003</v>
       </c>
       <c r="AJ293" t="s" s="2">
         <v>106</v>
@@ -40625,27 +40474,27 @@
         <v>81</v>
       </c>
       <c r="AN293" t="s" s="2">
-        <v>81</v>
+        <v>1004</v>
       </c>
       <c r="AO293" t="s" s="2">
-        <v>81</v>
+        <v>486</v>
       </c>
       <c r="AP293" t="s" s="2">
-        <v>975</v>
+        <v>81</v>
       </c>
       <c r="AQ293" t="s" s="2">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="AR293" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="294" hidden="true">
+    <row r="294">
       <c r="A294" t="s" s="2">
-        <v>976</v>
+        <v>1006</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>977</v>
+        <v>1006</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -40656,10 +40505,10 @@
         <v>82</v>
       </c>
       <c r="G294" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H294" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I294" t="s" s="2">
         <v>81</v>
@@ -40668,18 +40517,16 @@
         <v>95</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>135</v>
+        <v>1007</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>978</v>
+        <v>1008</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>979</v>
+        <v>1009</v>
       </c>
       <c r="N294" s="2"/>
-      <c r="O294" t="s" s="2">
-        <v>980</v>
-      </c>
+      <c r="O294" s="2"/>
       <c r="P294" t="s" s="2">
         <v>81</v>
       </c>
@@ -40727,16 +40574,16 @@
         <v>81</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>981</v>
+        <v>1006</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH294" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI294" t="s" s="2">
-        <v>982</v>
+        <v>1003</v>
       </c>
       <c r="AJ294" t="s" s="2">
         <v>106</v>
@@ -40757,21 +40604,21 @@
         <v>81</v>
       </c>
       <c r="AP294" t="s" s="2">
-        <v>975</v>
+        <v>81</v>
       </c>
       <c r="AQ294" t="s" s="2">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="AR294" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="295" hidden="true">
+    <row r="295">
       <c r="A295" t="s" s="2">
-        <v>983</v>
+        <v>1010</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>984</v>
+        <v>1010</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -40782,32 +40629,28 @@
         <v>82</v>
       </c>
       <c r="G295" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H295" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I295" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J295" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>169</v>
+        <v>1011</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>986</v>
-      </c>
-      <c r="N295" t="s" s="2">
-        <v>987</v>
-      </c>
-      <c r="O295" t="s" s="2">
-        <v>988</v>
-      </c>
+        <v>1013</v>
+      </c>
+      <c r="N295" s="2"/>
+      <c r="O295" s="2"/>
       <c r="P295" t="s" s="2">
         <v>81</v>
       </c>
@@ -40855,13 +40698,13 @@
         <v>81</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH295" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI295" t="s" s="2">
         <v>81</v>
@@ -40876,2274 +40719,26 @@
         <v>81</v>
       </c>
       <c r="AM295" t="s" s="2">
-        <v>81</v>
+        <v>1014</v>
       </c>
       <c r="AN295" t="s" s="2">
-        <v>81</v>
+        <v>1015</v>
       </c>
       <c r="AO295" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP295" t="s" s="2">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="AQ295" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR295" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="296" hidden="true">
-      <c r="A296" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="B296" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="C296" s="2"/>
-      <c r="D296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E296" s="2"/>
-      <c r="F296" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G296" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K296" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="L296" t="s" s="2">
-        <v>992</v>
-      </c>
-      <c r="M296" t="s" s="2">
-        <v>993</v>
-      </c>
-      <c r="N296" t="s" s="2">
-        <v>994</v>
-      </c>
-      <c r="O296" s="2"/>
-      <c r="P296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q296" s="2"/>
-      <c r="R296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF296" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="AG296" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH296" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI296" t="s" s="2">
-        <v>995</v>
-      </c>
-      <c r="AJ296" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP296" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ296" t="s" s="2">
-        <v>996</v>
-      </c>
-      <c r="AR296" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="B297" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="C297" s="2"/>
-      <c r="D297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E297" s="2"/>
-      <c r="F297" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G297" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H297" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J297" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K297" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L297" t="s" s="2">
-        <v>998</v>
-      </c>
-      <c r="M297" t="s" s="2">
-        <v>999</v>
-      </c>
-      <c r="N297" s="2"/>
-      <c r="O297" s="2"/>
-      <c r="P297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q297" s="2"/>
-      <c r="R297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF297" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="AG297" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH297" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ297" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM297" t="s" s="2">
-        <v>1000</v>
-      </c>
-      <c r="AN297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO297" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP297" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="AQ297" t="s" s="2">
-        <v>1002</v>
-      </c>
-      <c r="AR297" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="298" hidden="true">
-      <c r="A298" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="B298" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="C298" s="2"/>
-      <c r="D298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E298" s="2"/>
-      <c r="F298" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G298" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J298" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K298" t="s" s="2">
-        <v>1004</v>
-      </c>
-      <c r="L298" t="s" s="2">
-        <v>1005</v>
-      </c>
-      <c r="M298" t="s" s="2">
-        <v>1006</v>
-      </c>
-      <c r="N298" s="2"/>
-      <c r="O298" s="2"/>
-      <c r="P298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q298" s="2"/>
-      <c r="R298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF298" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="AG298" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH298" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ298" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP298" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ298" t="s" s="2">
-        <v>1007</v>
-      </c>
-      <c r="AR298" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="299" hidden="true">
-      <c r="A299" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="B299" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="C299" s="2"/>
-      <c r="D299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E299" s="2"/>
-      <c r="F299" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G299" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J299" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K299" t="s" s="2">
-        <v>1004</v>
-      </c>
-      <c r="L299" t="s" s="2">
-        <v>1009</v>
-      </c>
-      <c r="M299" t="s" s="2">
-        <v>1010</v>
-      </c>
-      <c r="N299" s="2"/>
-      <c r="O299" s="2"/>
-      <c r="P299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q299" s="2"/>
-      <c r="R299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF299" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="AG299" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH299" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ299" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO299" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP299" t="s" s="2">
-        <v>1011</v>
-      </c>
-      <c r="AQ299" t="s" s="2">
-        <v>1012</v>
-      </c>
-      <c r="AR299" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="300" hidden="true">
-      <c r="A300" t="s" s="2">
-        <v>1013</v>
-      </c>
-      <c r="B300" t="s" s="2">
-        <v>1013</v>
-      </c>
-      <c r="C300" s="2"/>
-      <c r="D300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E300" s="2"/>
-      <c r="F300" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G300" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K300" t="s" s="2">
-        <v>1014</v>
-      </c>
-      <c r="L300" t="s" s="2">
-        <v>1015</v>
-      </c>
-      <c r="M300" t="s" s="2">
-        <v>1016</v>
-      </c>
-      <c r="N300" s="2"/>
-      <c r="O300" s="2"/>
-      <c r="P300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q300" s="2"/>
-      <c r="R300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF300" t="s" s="2">
-        <v>1013</v>
-      </c>
-      <c r="AG300" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH300" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ300" t="s" s="2">
-        <v>1017</v>
-      </c>
-      <c r="AK300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ300" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR300" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="301" hidden="true">
-      <c r="A301" t="s" s="2">
-        <v>1018</v>
-      </c>
-      <c r="B301" t="s" s="2">
-        <v>1018</v>
-      </c>
-      <c r="C301" s="2"/>
-      <c r="D301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E301" s="2"/>
-      <c r="F301" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G301" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K301" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L301" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M301" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N301" s="2"/>
-      <c r="O301" s="2"/>
-      <c r="P301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q301" s="2"/>
-      <c r="R301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF301" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG301" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH301" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ301" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR301" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="302" hidden="true">
-      <c r="A302" t="s" s="2">
-        <v>1019</v>
-      </c>
-      <c r="B302" t="s" s="2">
-        <v>1019</v>
-      </c>
-      <c r="C302" s="2"/>
-      <c r="D302" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E302" s="2"/>
-      <c r="F302" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G302" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K302" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L302" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M302" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N302" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O302" s="2"/>
-      <c r="P302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q302" s="2"/>
-      <c r="R302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF302" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG302" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH302" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ302" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ302" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR302" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="303" hidden="true">
-      <c r="A303" t="s" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B303" t="s" s="2">
-        <v>1020</v>
-      </c>
-      <c r="C303" s="2"/>
-      <c r="D303" t="s" s="2">
-        <v>1021</v>
-      </c>
-      <c r="E303" s="2"/>
-      <c r="F303" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G303" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I303" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J303" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K303" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L303" t="s" s="2">
-        <v>1022</v>
-      </c>
-      <c r="M303" t="s" s="2">
-        <v>1023</v>
-      </c>
-      <c r="N303" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O303" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="P303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q303" s="2"/>
-      <c r="R303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF303" t="s" s="2">
-        <v>1024</v>
-      </c>
-      <c r="AG303" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH303" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ303" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ303" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR303" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="304" hidden="true">
-      <c r="A304" t="s" s="2">
-        <v>1025</v>
-      </c>
-      <c r="B304" t="s" s="2">
-        <v>1025</v>
-      </c>
-      <c r="C304" s="2"/>
-      <c r="D304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E304" s="2"/>
-      <c r="F304" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G304" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K304" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L304" t="s" s="2">
-        <v>1026</v>
-      </c>
-      <c r="M304" t="s" s="2">
-        <v>1027</v>
-      </c>
-      <c r="N304" s="2"/>
-      <c r="O304" s="2"/>
-      <c r="P304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q304" s="2"/>
-      <c r="R304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X304" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y304" t="s" s="2">
-        <v>1028</v>
-      </c>
-      <c r="Z304" t="s" s="2">
-        <v>1029</v>
-      </c>
-      <c r="AA304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF304" t="s" s="2">
-        <v>1025</v>
-      </c>
-      <c r="AG304" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH304" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI304" t="s" s="2">
-        <v>1030</v>
-      </c>
-      <c r="AJ304" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO304" t="s" s="2">
-        <v>1031</v>
-      </c>
-      <c r="AP304" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AQ304" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR304" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="305" hidden="true">
-      <c r="A305" t="s" s="2">
-        <v>1032</v>
-      </c>
-      <c r="B305" t="s" s="2">
-        <v>1032</v>
-      </c>
-      <c r="C305" s="2"/>
-      <c r="D305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E305" s="2"/>
-      <c r="F305" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G305" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K305" t="s" s="2">
-        <v>1033</v>
-      </c>
-      <c r="L305" t="s" s="2">
-        <v>1034</v>
-      </c>
-      <c r="M305" t="s" s="2">
-        <v>1035</v>
-      </c>
-      <c r="N305" s="2"/>
-      <c r="O305" s="2"/>
-      <c r="P305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q305" s="2"/>
-      <c r="R305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF305" t="s" s="2">
-        <v>1032</v>
-      </c>
-      <c r="AG305" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH305" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI305" t="s" s="2">
-        <v>1030</v>
-      </c>
-      <c r="AJ305" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ305" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR305" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="306" hidden="true">
-      <c r="A306" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="B306" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="C306" s="2"/>
-      <c r="D306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E306" s="2"/>
-      <c r="F306" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G306" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K306" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L306" t="s" s="2">
-        <v>1037</v>
-      </c>
-      <c r="M306" t="s" s="2">
-        <v>1038</v>
-      </c>
-      <c r="N306" s="2"/>
-      <c r="O306" s="2"/>
-      <c r="P306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q306" s="2"/>
-      <c r="R306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X306" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y306" t="s" s="2">
-        <v>1039</v>
-      </c>
-      <c r="Z306" t="s" s="2">
-        <v>1040</v>
-      </c>
-      <c r="AA306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF306" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="AG306" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH306" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ306" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ306" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR306" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="s" s="2">
-        <v>1041</v>
-      </c>
-      <c r="B307" t="s" s="2">
-        <v>1041</v>
-      </c>
-      <c r="C307" s="2"/>
-      <c r="D307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E307" s="2"/>
-      <c r="F307" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G307" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H307" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K307" t="s" s="2">
-        <v>1014</v>
-      </c>
-      <c r="L307" t="s" s="2">
-        <v>1042</v>
-      </c>
-      <c r="M307" t="s" s="2">
-        <v>1043</v>
-      </c>
-      <c r="N307" t="s" s="2">
-        <v>1044</v>
-      </c>
-      <c r="O307" s="2"/>
-      <c r="P307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q307" s="2"/>
-      <c r="R307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF307" t="s" s="2">
-        <v>1041</v>
-      </c>
-      <c r="AG307" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH307" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ307" t="s" s="2">
-        <v>1045</v>
-      </c>
-      <c r="AK307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ307" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR307" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="308" hidden="true">
-      <c r="A308" t="s" s="2">
-        <v>1046</v>
-      </c>
-      <c r="B308" t="s" s="2">
-        <v>1046</v>
-      </c>
-      <c r="C308" s="2"/>
-      <c r="D308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E308" s="2"/>
-      <c r="F308" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G308" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K308" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L308" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M308" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N308" s="2"/>
-      <c r="O308" s="2"/>
-      <c r="P308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q308" s="2"/>
-      <c r="R308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF308" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG308" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH308" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ308" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR308" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="309" hidden="true">
-      <c r="A309" t="s" s="2">
-        <v>1047</v>
-      </c>
-      <c r="B309" t="s" s="2">
-        <v>1047</v>
-      </c>
-      <c r="C309" s="2"/>
-      <c r="D309" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E309" s="2"/>
-      <c r="F309" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G309" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K309" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L309" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M309" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N309" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O309" s="2"/>
-      <c r="P309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q309" s="2"/>
-      <c r="R309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF309" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG309" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH309" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ309" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ309" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR309" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="310" hidden="true">
-      <c r="A310" t="s" s="2">
-        <v>1048</v>
-      </c>
-      <c r="B310" t="s" s="2">
-        <v>1048</v>
-      </c>
-      <c r="C310" s="2"/>
-      <c r="D310" t="s" s="2">
-        <v>1021</v>
-      </c>
-      <c r="E310" s="2"/>
-      <c r="F310" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G310" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I310" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J310" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K310" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L310" t="s" s="2">
-        <v>1022</v>
-      </c>
-      <c r="M310" t="s" s="2">
-        <v>1023</v>
-      </c>
-      <c r="N310" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O310" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="P310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q310" s="2"/>
-      <c r="R310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF310" t="s" s="2">
-        <v>1024</v>
-      </c>
-      <c r="AG310" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH310" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ310" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ310" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR310" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="311" hidden="true">
-      <c r="A311" t="s" s="2">
-        <v>1049</v>
-      </c>
-      <c r="B311" t="s" s="2">
-        <v>1049</v>
-      </c>
-      <c r="C311" s="2"/>
-      <c r="D311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E311" s="2"/>
-      <c r="F311" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G311" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J311" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K311" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L311" t="s" s="2">
-        <v>1050</v>
-      </c>
-      <c r="M311" t="s" s="2">
-        <v>1051</v>
-      </c>
-      <c r="N311" s="2"/>
-      <c r="O311" s="2"/>
-      <c r="P311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q311" s="2"/>
-      <c r="R311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X311" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y311" t="s" s="2">
-        <v>1052</v>
-      </c>
-      <c r="Z311" t="s" s="2">
-        <v>1053</v>
-      </c>
-      <c r="AA311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF311" t="s" s="2">
-        <v>1049</v>
-      </c>
-      <c r="AG311" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH311" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI311" t="s" s="2">
-        <v>1054</v>
-      </c>
-      <c r="AJ311" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN311" t="s" s="2">
-        <v>1055</v>
-      </c>
-      <c r="AO311" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AP311" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ311" t="s" s="2">
-        <v>1056</v>
-      </c>
-      <c r="AR311" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="s" s="2">
-        <v>1057</v>
-      </c>
-      <c r="B312" t="s" s="2">
-        <v>1057</v>
-      </c>
-      <c r="C312" s="2"/>
-      <c r="D312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E312" s="2"/>
-      <c r="F312" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G312" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H312" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J312" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K312" t="s" s="2">
-        <v>1058</v>
-      </c>
-      <c r="L312" t="s" s="2">
-        <v>1059</v>
-      </c>
-      <c r="M312" t="s" s="2">
-        <v>1060</v>
-      </c>
-      <c r="N312" s="2"/>
-      <c r="O312" s="2"/>
-      <c r="P312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q312" s="2"/>
-      <c r="R312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF312" t="s" s="2">
-        <v>1057</v>
-      </c>
-      <c r="AG312" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH312" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI312" t="s" s="2">
-        <v>1054</v>
-      </c>
-      <c r="AJ312" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP312" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ312" t="s" s="2">
-        <v>1056</v>
-      </c>
-      <c r="AR312" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="s" s="2">
-        <v>1061</v>
-      </c>
-      <c r="B313" t="s" s="2">
-        <v>1061</v>
-      </c>
-      <c r="C313" s="2"/>
-      <c r="D313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E313" s="2"/>
-      <c r="F313" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G313" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H313" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K313" t="s" s="2">
-        <v>1062</v>
-      </c>
-      <c r="L313" t="s" s="2">
-        <v>1063</v>
-      </c>
-      <c r="M313" t="s" s="2">
-        <v>1064</v>
-      </c>
-      <c r="N313" s="2"/>
-      <c r="O313" s="2"/>
-      <c r="P313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q313" s="2"/>
-      <c r="R313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF313" t="s" s="2">
-        <v>1061</v>
-      </c>
-      <c r="AG313" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH313" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ313" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM313" t="s" s="2">
-        <v>1065</v>
-      </c>
-      <c r="AN313" t="s" s="2">
-        <v>1066</v>
-      </c>
-      <c r="AO313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP313" t="s" s="2">
-        <v>1067</v>
-      </c>
-      <c r="AQ313" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR313" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR313">
+  <autoFilter ref="A1:AR295">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -43153,7 +40748,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI312">
+  <conditionalFormatting sqref="A2:AI294">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:44:38+00:00</t>
+    <t>2026-10-19T22:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-diagnose-primaertumor.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:30:48+00:00</t>
+    <t>2026-10-19T23:12:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
